--- a/InputData/elec/GBCGpUNR/Grid Bat Cap Growth per Unit Net Revenue.xlsx
+++ b/InputData/elec/GBCGpUNR/Grid Bat Cap Growth per Unit Net Revenue.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\GBCGpUNR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\GBCGpUNR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C74A81D-3725-4C8A-8875-8C49E5853CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DD937F-49CA-4BA4-9FFA-768D6AF24171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-1185" windowWidth="24240" windowHeight="13140" xr2:uid="{7E47E401-4FF2-4F75-986A-BA871D3584BD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{7E47E401-4FF2-4F75-986A-BA871D3584BD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -130,9 +130,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -170,7 +170,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -276,7 +276,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -418,7 +418,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -476,7 +476,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>2000</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -644,13 +644,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80411482-3296-46E6-9ECC-35374C6A4170}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80411482-3296-46E6-9ECC-35374C6A4170}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09A5A398-8CE6-4F1C-8934-C030A6CE9040}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09A5A398-8CE6-4F1C-8934-C030A6CE9040}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62906E83-68FD-4D34-BC9C-03A79265EE1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62906E83-68FD-4D34-BC9C-03A79265EE1B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>